--- a/Testing/Test_Plan.xlsx
+++ b/Testing/Test_Plan.xlsx
@@ -1,17 +1,49 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <sheets>
-    <sheet sheetId="1" name="Test Plan" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="KPI Summary" state="visible" r:id="rId5"/>
-  </sheets>
-  <calcPr calcId="171027"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>2</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="2" baseType="lpstr">
+      <vt:lpstr>Test Plan</vt:lpstr>
+      <vt:lpstr>KPI Summary</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <Manager/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>Unknown</dc:creator>
+  <dc:title/>
+  <dc:subject/>
+  <dc:description/>
+  <cp:keywords/>
+  <cp:category/>
+  <cp:lastModifiedBy>Unknown</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-31T01:36:24Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-31T01:36:24Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
   <si>
     <t>Test</t>
@@ -92,16 +124,16 @@
     <t>Test 5</t>
   </si>
   <si>
-    <t>Receiver/control validation</t>
-  </si>
-  <si>
-    <t>Confirm all RC channels respond correctly in Betaflight receiver tab, including the payload AUX channel</t>
-  </si>
-  <si>
-    <t>All channels move correctly end-to-end, AUX channel triggers servo output</t>
-  </si>
-  <si>
-    <t>TARGET: all channels pass</t>
+    <t>RC-link validation (custom ESP32 link)</t>
+  </si>
+  <si>
+    <t>Confirm all RC channels respond correctly in Betaflight receiver tab, including the payload AUX channel; then walk the TX out of ESP-NOW range (or power it off) and confirm the RX ESP32's failsafe watchdog triggers correctly within its timeout</t>
+  </si>
+  <si>
+    <t>All channels move correctly end-to-end, AUX channel triggers servo output, and the FC shows a failsafe condition (not stale/held values) within the RX firmware's timeout when the link is lost</t>
+  </si>
+  <si>
+    <t>TARGET: all channels pass, failsafe verified</t>
   </si>
   <si>
     <t>Test 6</t>
@@ -259,7 +291,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -318,7 +350,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -638,7 +670,19 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <sheets>
+    <sheet sheetId="1" name="Test Plan" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="KPI Summary" state="visible" r:id="rId5"/>
+  </sheets>
+  <calcPr calcId="171027"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -843,7 +887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>

--- a/Testing/Test_Plan.xlsx
+++ b/Testing/Test_Plan.xlsx
@@ -1,49 +1,17 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>2</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="2" baseType="lpstr">
-      <vt:lpstr>Test Plan</vt:lpstr>
-      <vt:lpstr>KPI Summary</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <Company/>
-  <Manager/>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>16.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <sheets>
+    <sheet sheetId="1" name="Test Plan" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="KPI Summary" state="visible" r:id="rId5"/>
+  </sheets>
+  <calcPr calcId="171027"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>Unknown</dc:creator>
-  <dc:title/>
-  <dc:subject/>
-  <dc:description/>
-  <cp:keywords/>
-  <cp:category/>
-  <cp:lastModifiedBy>Unknown</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-31T01:36:24Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-31T01:36:24Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
   <si>
     <t>Test</t>
@@ -291,7 +259,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -350,7 +318,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -670,19 +638,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <sheets>
-    <sheet sheetId="1" name="Test Plan" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="KPI Summary" state="visible" r:id="rId5"/>
-  </sheets>
-  <calcPr calcId="171027"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -887,7 +843,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
